--- a/agriculture 25.xlsx
+++ b/agriculture 25.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -131,6 +131,9 @@
   </si>
   <si>
     <t xml:space="preserve">2019-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit:- </t>
   </si>
   <si>
     <t xml:space="preserve">Source:Directorate of Economics &amp; Statistics( APY statistics 1998-99 to 2019-20)</t>
@@ -144,7 +147,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -174,6 +177,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -249,7 +258,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -270,7 +279,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O1048576"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="46.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1325,28 +1334,48 @@
         <v>-5.33333333333333</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A24:N24"/>
+  <mergeCells count="2">
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A25:O25"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>

--- a/agriculture 25.xlsx
+++ b/agriculture 25.xlsx
@@ -133,7 +133,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage(%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source:Directorate of Economics &amp; Statistics( APY statistics 1998-99 to 2019-20)</t>
@@ -147,7 +147,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -177,12 +177,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -258,7 +252,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/agriculture 25.xlsx
+++ b/agriculture 25.xlsx
@@ -133,7 +133,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- Percentage(%)</t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source:Directorate of Economics &amp; Statistics( APY statistics 1998-99 to 2019-20)</t>
